--- a/contoh_import_siswa.xlsx
+++ b/contoh_import_siswa.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ABSENSI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ACCB63-914E-4D34-9B28-9BE73E0D1E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B3CFFF-7025-4154-89F4-88E0DD4B8A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Siswa" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="207">
   <si>
     <t>nis</t>
   </si>
@@ -46,29 +59,608 @@
     <t>XII RPL 2</t>
   </si>
   <si>
-    <t>Oman</t>
-  </si>
-  <si>
-    <t>oman@sekolah.test</t>
-  </si>
-  <si>
-    <t>ohim@sekolah.test</t>
-  </si>
-  <si>
-    <t>Ohim</t>
-  </si>
-  <si>
-    <t>Deni</t>
-  </si>
-  <si>
-    <t>deni@sekolah.test</t>
+    <t>24.25.X.613</t>
+  </si>
+  <si>
+    <t>24.25.X.614</t>
+  </si>
+  <si>
+    <t>24.25.X.615</t>
+  </si>
+  <si>
+    <t>24.25.X.616</t>
+  </si>
+  <si>
+    <t>24.25.X.617</t>
+  </si>
+  <si>
+    <t>24.25.X.618</t>
+  </si>
+  <si>
+    <t>24.25.X.619</t>
+  </si>
+  <si>
+    <t>24.25.X.620</t>
+  </si>
+  <si>
+    <t>24.25.X.622</t>
+  </si>
+  <si>
+    <t>24.25.X.623</t>
+  </si>
+  <si>
+    <t>24.25.X.625</t>
+  </si>
+  <si>
+    <t>24.25.X.626</t>
+  </si>
+  <si>
+    <t>24.25.X.627</t>
+  </si>
+  <si>
+    <t>24.25.X.629</t>
+  </si>
+  <si>
+    <t>24.25.X.630</t>
+  </si>
+  <si>
+    <t>24.25.X.631</t>
+  </si>
+  <si>
+    <t>24.25.X.632</t>
+  </si>
+  <si>
+    <t>24.25.X.633</t>
+  </si>
+  <si>
+    <t>24.25.X.634</t>
+  </si>
+  <si>
+    <t>24.25.X.635</t>
+  </si>
+  <si>
+    <t>24.25.X.636</t>
+  </si>
+  <si>
+    <t>24.25.X.637</t>
+  </si>
+  <si>
+    <t>24.25.X.638</t>
+  </si>
+  <si>
+    <t>24.25.X.639</t>
+  </si>
+  <si>
+    <t>24.25.X.640</t>
+  </si>
+  <si>
+    <t>24.25.X.641</t>
+  </si>
+  <si>
+    <t>24.25.X.642</t>
+  </si>
+  <si>
+    <t>24.25.X.644</t>
+  </si>
+  <si>
+    <t>24.25.X.645</t>
+  </si>
+  <si>
+    <t>24.25.X.646</t>
+  </si>
+  <si>
+    <t>24.25.X.647</t>
+  </si>
+  <si>
+    <t>24.25.X.648</t>
+  </si>
+  <si>
+    <t>24.25.X.649</t>
+  </si>
+  <si>
+    <t>24.25.X.650</t>
+  </si>
+  <si>
+    <t>24.25.X.651</t>
+  </si>
+  <si>
+    <t>24.25.X.652</t>
+  </si>
+  <si>
+    <t>24.25.X.653</t>
+  </si>
+  <si>
+    <t>24.25.X.654</t>
+  </si>
+  <si>
+    <t>24.25.X.655</t>
+  </si>
+  <si>
+    <t>24.25.X.656</t>
+  </si>
+  <si>
+    <t>24.25.X.657</t>
+  </si>
+  <si>
+    <t>24.25.X.658</t>
+  </si>
+  <si>
+    <t>24.25.X.659</t>
+  </si>
+  <si>
+    <t>24.25.X.660</t>
+  </si>
+  <si>
+    <t>24.25.X.661</t>
+  </si>
+  <si>
+    <t>24.25.X.662</t>
+  </si>
+  <si>
+    <t>24.25.X.663</t>
+  </si>
+  <si>
+    <t>24.25.X.665</t>
+  </si>
+  <si>
+    <t>24.25.X.666</t>
+  </si>
+  <si>
+    <t>24.25.X.667</t>
+  </si>
+  <si>
+    <t>24.25.X.668</t>
+  </si>
+  <si>
+    <t>24.25.X.669</t>
+  </si>
+  <si>
+    <t>24.25.X.670</t>
+  </si>
+  <si>
+    <t>24.25.X.671</t>
+  </si>
+  <si>
+    <t>24.25.X.672</t>
+  </si>
+  <si>
+    <t>24.25.X.673</t>
+  </si>
+  <si>
+    <t>24.25.X.675</t>
+  </si>
+  <si>
+    <t>24.25.X.676</t>
+  </si>
+  <si>
+    <t>24.25.X.677</t>
+  </si>
+  <si>
+    <t>24.25.X.678</t>
+  </si>
+  <si>
+    <t>24.25.X.679</t>
+  </si>
+  <si>
+    <t>24.25.X.680</t>
+  </si>
+  <si>
+    <t>24.25.X.681</t>
+  </si>
+  <si>
+    <t>24.25.X.682</t>
+  </si>
+  <si>
+    <t>24.25.X.683</t>
+  </si>
+  <si>
+    <t>24.25.X.684</t>
+  </si>
+  <si>
+    <t>AHSAN MAHMUD FAUZI YUSRY</t>
+  </si>
+  <si>
+    <t>AIDA SAHARAWATI</t>
+  </si>
+  <si>
+    <t>BANGKIT FAIZ SYARIFUDDIN</t>
+  </si>
+  <si>
+    <t>CAHYA MUHAMAD RIFAN</t>
+  </si>
+  <si>
+    <t>DESTIKA</t>
+  </si>
+  <si>
+    <t>EKA OSA PRASETYO</t>
+  </si>
+  <si>
+    <t>FAHRI AL FAUZI</t>
+  </si>
+  <si>
+    <t>FIKRI RIDWANULLOH</t>
+  </si>
+  <si>
+    <t>HAFIDZ FAYYADH ARKAN</t>
+  </si>
+  <si>
+    <t>HANIF AKMA AZIB</t>
+  </si>
+  <si>
+    <t>MUHAMAD DAFFA RAFASYA</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RIZKI RAMADHAN</t>
+  </si>
+  <si>
+    <t>NAAILA LUTHFI NAFIISA</t>
+  </si>
+  <si>
+    <t>NUR JAMILAH</t>
+  </si>
+  <si>
+    <t>PASHYA PRASETYO WIBOWO</t>
+  </si>
+  <si>
+    <t>PUTRI NABILA RAMADHANI</t>
+  </si>
+  <si>
+    <t>RAFLI MUHAMMAD GHOJALI</t>
+  </si>
+  <si>
+    <t>RAKA FAIZA BILLAH</t>
+  </si>
+  <si>
+    <t>RAY SAJUTA PRAJA</t>
+  </si>
+  <si>
+    <t>REVA AYUNADIA</t>
+  </si>
+  <si>
+    <t>REZQI MAULANA YUSUP</t>
+  </si>
+  <si>
+    <t>RIANTO</t>
+  </si>
+  <si>
+    <t>RIDWAN FHATURROHMAN</t>
+  </si>
+  <si>
+    <t>RIFA AULIA DAMAYANTI</t>
+  </si>
+  <si>
+    <t>RIZKIA SUCI RAMADHANI</t>
+  </si>
+  <si>
+    <t>SARAH SABILA KHOERUNNISA</t>
+  </si>
+  <si>
+    <t>SOFYAN RAFI ISKANDAR</t>
+  </si>
+  <si>
+    <t>TIA APRILIA KUSWARA</t>
+  </si>
+  <si>
+    <t>TIARA SULISTIA NINGRUM</t>
+  </si>
+  <si>
+    <t>VIVI HANIFAH FEBRIYANTI</t>
+  </si>
+  <si>
+    <t>WULAN KARTIKA SARI</t>
+  </si>
+  <si>
+    <t>ZAIDAN HASBI AKBAR</t>
+  </si>
+  <si>
+    <t>ABHIPRAYA SAMBOGA</t>
+  </si>
+  <si>
+    <t>AGUS RIZKY NURFADIL</t>
+  </si>
+  <si>
+    <t>ALIFAH DZAAKIROH</t>
+  </si>
+  <si>
+    <t>ALYA FUTRI SALSABILA</t>
+  </si>
+  <si>
+    <t>ARIF WIJAKSANA</t>
+  </si>
+  <si>
+    <t>CHERYL PUTRI RAHMADYA</t>
+  </si>
+  <si>
+    <t>DANDI RIZIQ KAHARUDIN</t>
+  </si>
+  <si>
+    <t>DEVI NURUL AZIZAH</t>
+  </si>
+  <si>
+    <t>DHINDA PUTRI ARYANI</t>
+  </si>
+  <si>
+    <t>DINDA ZAHRA NUR AFIFAH</t>
+  </si>
+  <si>
+    <t>FULAN MUHAMMAD</t>
+  </si>
+  <si>
+    <t>IQBAL MAULANA SIDIK</t>
+  </si>
+  <si>
+    <t>KURNIAWAN SUDRAJAT</t>
+  </si>
+  <si>
+    <t>LUTHFI NUR ZAIDAN</t>
+  </si>
+  <si>
+    <t>M. IHSAN ATHALLAH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ARDAN ZAQUAN AL KAHFI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FARHAN NASRULLAH</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RIFKY FAUZIA SHONHAJI</t>
+  </si>
+  <si>
+    <t>NABILA AINUN AL ZAHRANI</t>
+  </si>
+  <si>
+    <t>NAUVAL EAGAN PURNAMA</t>
+  </si>
+  <si>
+    <t>NIA KARUNIA</t>
+  </si>
+  <si>
+    <t>NOVA PUSPITASARI</t>
+  </si>
+  <si>
+    <t>RAFLY NOVIADY</t>
+  </si>
+  <si>
+    <t>RAKA</t>
+  </si>
+  <si>
+    <t>RIKA NOVIYANTIKA</t>
+  </si>
+  <si>
+    <t>RIKI</t>
+  </si>
+  <si>
+    <t>RINRIN RINAWATI</t>
+  </si>
+  <si>
+    <t>RIRIN DWI RIYANTO</t>
+  </si>
+  <si>
+    <t>RISMA RISTIANTI</t>
+  </si>
+  <si>
+    <t>RIZKY RAMADANI</t>
+  </si>
+  <si>
+    <t>SOLEH WAHYUDIN</t>
+  </si>
+  <si>
+    <t>SRIYANTI DEVIE</t>
+  </si>
+  <si>
+    <t>TALITA APRILIANA</t>
+  </si>
+  <si>
+    <t>WILLY HAFFIDIN</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>ahsan@sekolah.test</t>
+  </si>
+  <si>
+    <t>aida@sekolai.test</t>
+  </si>
+  <si>
+    <t>bangkit@sekolba.test</t>
+  </si>
+  <si>
+    <t>cahya@sekolca.test</t>
+  </si>
+  <si>
+    <t>destika@sekopde.test</t>
+  </si>
+  <si>
+    <t>eka@sekolek.test</t>
+  </si>
+  <si>
+    <t>fahri@sekolfa.test</t>
+  </si>
+  <si>
+    <t>fikri@sekolfi.test</t>
+  </si>
+  <si>
+    <t>hafidz@sekolha.test</t>
+  </si>
+  <si>
+    <t>hanif@sekolha.test</t>
+  </si>
+  <si>
+    <t>daffa@sekolah.test</t>
+  </si>
+  <si>
+    <t>rizki@sekolah.test</t>
+  </si>
+  <si>
+    <t>luthfi@sekopah.test</t>
+  </si>
+  <si>
+    <t>nur@sekopah.test</t>
+  </si>
+  <si>
+    <t>prasetyo@sekolah.test</t>
+  </si>
+  <si>
+    <t>nabila@sekopah.test</t>
+  </si>
+  <si>
+    <t>muhammad@sekolah.test</t>
+  </si>
+  <si>
+    <t>faiza@sekolah.test</t>
+  </si>
+  <si>
+    <t>sajuta@sekolah.test</t>
+  </si>
+  <si>
+    <t>reva@sekopah.test</t>
+  </si>
+  <si>
+    <t>maulana@sekolah.test</t>
+  </si>
+  <si>
+    <t>ridwan@sekolah.test</t>
+  </si>
+  <si>
+    <t>aulia@sekopah.test</t>
+  </si>
+  <si>
+    <t>suci@sekopah.test</t>
+  </si>
+  <si>
+    <t>sabila@sekopah.test</t>
+  </si>
+  <si>
+    <t>rafi@sekolah.test</t>
+  </si>
+  <si>
+    <t>aprilia@sekopah.test</t>
+  </si>
+  <si>
+    <t>sulistia@sekopah.test</t>
+  </si>
+  <si>
+    <t>hanifah@sekopah.test</t>
+  </si>
+  <si>
+    <t>kartika@sekopah.test</t>
+  </si>
+  <si>
+    <t>hasbi@sekolah.test</t>
+  </si>
+  <si>
+    <t>abhipraya@sekolah.test</t>
+  </si>
+  <si>
+    <t>rizky@sekolah.test</t>
+  </si>
+  <si>
+    <t>alifah@sekopah.test</t>
+  </si>
+  <si>
+    <t>futri@sekopah.test</t>
+  </si>
+  <si>
+    <t>arif@sekolah.test</t>
+  </si>
+  <si>
+    <t>putri@sekopah.test</t>
+  </si>
+  <si>
+    <t>riziq@sekolah.test</t>
+  </si>
+  <si>
+    <t>nurul@sekopah.test</t>
+  </si>
+  <si>
+    <t>fulan@sekolah.test</t>
+  </si>
+  <si>
+    <t>kurniawan@sekolah.test</t>
+  </si>
+  <si>
+    <t>nur@sekolah.test</t>
+  </si>
+  <si>
+    <t>ihsan@sekolah.test</t>
+  </si>
+  <si>
+    <t>al@sekolah.test</t>
+  </si>
+  <si>
+    <t>farhan@sekolah.test</t>
+  </si>
+  <si>
+    <t>fauzia@sekolah.test</t>
+  </si>
+  <si>
+    <t>al@sekopah.test</t>
+  </si>
+  <si>
+    <t>eagan@sekolah.test</t>
+  </si>
+  <si>
+    <t>nia@sekopah.test</t>
+  </si>
+  <si>
+    <t>nova@sekopah.test</t>
+  </si>
+  <si>
+    <t>rafly@sekolah.test</t>
+  </si>
+  <si>
+    <t>rinrin@sekopah.test</t>
+  </si>
+  <si>
+    <t>soleh@sekolah.test</t>
+  </si>
+  <si>
+    <t>talita@sekopah.test</t>
+  </si>
+  <si>
+    <t>willy@sekolah.test</t>
+  </si>
+  <si>
+    <t>rianto@sekolah.test</t>
+  </si>
+  <si>
+    <t>dindanur@sekopah.test</t>
+  </si>
+  <si>
+    <t>dindaputri@sekopah.test</t>
+  </si>
+  <si>
+    <t>iqbalmaulana@sekolah.test</t>
+  </si>
+  <si>
+    <t>raka@sekolah.test</t>
+  </si>
+  <si>
+    <t>riki@sekolah.test</t>
+  </si>
+  <si>
+    <t>rika@sekolah.test</t>
+  </si>
+  <si>
+    <t>dwi@sekolah.test</t>
+  </si>
+  <si>
+    <t>risma@sekolah.test</t>
+  </si>
+  <si>
+    <t>sriyanti@sekolah.test</t>
+  </si>
+  <si>
+    <t>rizkyramdan@sekolah.test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,16 +676,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,14 +716,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -412,8 +1053,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -433,61 +1078,1207 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2113321</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1124521</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2211451</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
+      <c r="B7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>140</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C53" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="4"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E70" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{1BC33A60-8F40-4C73-8BC6-317E2E2C5F2D}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{B719AF41-2ADB-4586-87EF-F734E5FC6677}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{FDDDAC28-96FF-44C4-9E39-B8BFFD4A1C1B}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{7EB3DDCC-6EF7-4545-8DFC-69122B08A99F}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{EDE1F7D0-B71A-440A-89AC-09C4ED5D943B}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{2B4F47B0-202C-4FF6-8A35-4C90355AF287}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{6177883D-B150-4601-9049-61491D4BA8B8}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{47DA9D43-A089-4F06-BA76-88E45614BC61}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{2089E446-7FE7-4CC3-B584-A1B81369DB98}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{D0F0862A-8809-4EF8-8154-F545B1966ACF}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{A7AD2A90-0A6E-4E35-B56C-271E5C4157FF}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{A48EA1E3-B021-4DFE-90DC-39782995931F}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{C1D53784-CC3B-4EC6-BDA8-3FDCAE7EFCCE}"/>
+    <hyperlink ref="D13" r:id="rId11" xr:uid="{91772C6C-F722-4DB5-8B72-8FBE85884B5F}"/>
+    <hyperlink ref="D14" r:id="rId12" xr:uid="{2D1F57E9-F125-45BE-A7BA-429408DA81EF}"/>
+    <hyperlink ref="D15" r:id="rId13" xr:uid="{5F4EC067-A8F0-40E5-9920-4895D0868CCD}"/>
+    <hyperlink ref="D16" r:id="rId14" xr:uid="{3A6F52D9-2318-4096-A10E-131124DE766E}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{24E20BB4-5F42-419C-B376-045F68939D95}"/>
+    <hyperlink ref="D18" r:id="rId16" xr:uid="{2F0ACEC5-3C7A-43E7-8A34-4E4C54678F2D}"/>
+    <hyperlink ref="D19" r:id="rId17" xr:uid="{D50DA250-36BA-41AE-A98B-A7A426AF2C6B}"/>
+    <hyperlink ref="D20" r:id="rId18" xr:uid="{CCCCBA7D-611D-47B5-863F-8F0B66EFD0EB}"/>
+    <hyperlink ref="D21" r:id="rId19" xr:uid="{13EF5196-0AA6-4D7C-8822-73228E1B67C5}"/>
+    <hyperlink ref="D22" r:id="rId20" xr:uid="{426DE94D-A74B-4EC1-88A3-84CB6B79EB1E}"/>
+    <hyperlink ref="D23" r:id="rId21" xr:uid="{1266A6A3-C329-4D7B-A158-3FCCD6630EC6}"/>
+    <hyperlink ref="D25" r:id="rId22" xr:uid="{C2983C18-92A4-4944-B958-D51ED6BD91F2}"/>
+    <hyperlink ref="D26" r:id="rId23" xr:uid="{C9EADC5E-DCF0-4312-9E25-AEBFCAE96DF9}"/>
+    <hyperlink ref="D27" r:id="rId24" xr:uid="{C8D518D2-1AE8-45F5-B58A-E39176922187}"/>
+    <hyperlink ref="D28" r:id="rId25" xr:uid="{6996C546-1215-4E30-BB10-425EDAFD4A96}"/>
+    <hyperlink ref="D29" r:id="rId26" xr:uid="{EE729EA0-0C6E-43BA-A342-F1DD3A5DE821}"/>
+    <hyperlink ref="D30" r:id="rId27" xr:uid="{00977EAE-C625-4191-857C-A8C076288B9E}"/>
+    <hyperlink ref="D31" r:id="rId28" xr:uid="{69B8E2F0-BBE3-4DC0-ACD7-083AAB742340}"/>
+    <hyperlink ref="D32" r:id="rId29" xr:uid="{433F66D8-B21D-4D7E-B731-F0507750DFFA}"/>
+    <hyperlink ref="D33" r:id="rId30" xr:uid="{B6AAA8C6-4A75-4F75-84AE-28733B4239BC}"/>
+    <hyperlink ref="D34" r:id="rId31" xr:uid="{E46BE7C4-AE6A-497F-A11C-4F559C7D0480}"/>
+    <hyperlink ref="D35" r:id="rId32" xr:uid="{8BBF2D99-7897-4DB1-9338-8780CBE35EA1}"/>
+    <hyperlink ref="D36" r:id="rId33" xr:uid="{B461ED45-E457-4372-A9C5-19FA9050923B}"/>
+    <hyperlink ref="D37" r:id="rId34" xr:uid="{DAFF96FB-D125-468E-B08D-6FE10AA77F74}"/>
+    <hyperlink ref="D38" r:id="rId35" xr:uid="{896B4888-9C5B-4856-BFC6-F33043A6763E}"/>
+    <hyperlink ref="D39" r:id="rId36" xr:uid="{8D1439F4-837B-4A03-A359-C371ABF50310}"/>
+    <hyperlink ref="D40" r:id="rId37" xr:uid="{00893B37-D1F1-46E6-A7DD-4EA3FA412EC9}"/>
+    <hyperlink ref="D41" r:id="rId38" xr:uid="{BB2AFCBD-1841-4AC4-B243-20BC712CF1BA}"/>
+    <hyperlink ref="D42" r:id="rId39" xr:uid="{5E3948D8-15EE-4218-9701-A42111FF621B}"/>
+    <hyperlink ref="D43" r:id="rId40" xr:uid="{9FF63BF8-7810-4A97-B3AD-EBA4462C48A0}"/>
+    <hyperlink ref="D44" r:id="rId41" xr:uid="{AF9F70EC-658B-4FE4-8C95-B282815D066C}"/>
+    <hyperlink ref="D45" r:id="rId42" xr:uid="{E51211FD-FC79-4C1A-9AF0-31540EDD2AE3}"/>
+    <hyperlink ref="D46" r:id="rId43" xr:uid="{F0A857E3-E860-4A81-B9EA-BF24021A190C}"/>
+    <hyperlink ref="D47" r:id="rId44" xr:uid="{67318978-BBFB-4432-B58B-68A4095546D9}"/>
+    <hyperlink ref="D48" r:id="rId45" xr:uid="{E4B85D74-EA2C-4AB8-821A-E78FDBE3B433}"/>
+    <hyperlink ref="D49" r:id="rId46" xr:uid="{F50F9B97-8B8E-4A68-B28B-9343E684ACC3}"/>
+    <hyperlink ref="D50" r:id="rId47" xr:uid="{5F902341-AC3D-49AB-9F17-5731F6B1402B}"/>
+    <hyperlink ref="D51" r:id="rId48" xr:uid="{868B1532-53FB-4915-A918-13B7CDC7C9D8}"/>
+    <hyperlink ref="D52" r:id="rId49" xr:uid="{E7414DA4-82F4-4DB0-ACFF-8B87FAA280C4}"/>
+    <hyperlink ref="D53" r:id="rId50" xr:uid="{E8E7FCC3-61EB-4DE0-840C-CAD0B4826FCE}"/>
+    <hyperlink ref="D54" r:id="rId51" xr:uid="{32A7B2A4-F2BA-4B92-955C-D33A1161689F}"/>
+    <hyperlink ref="D55" r:id="rId52" xr:uid="{DAF2B73F-E347-4691-8B03-35B6E9260DC9}"/>
+    <hyperlink ref="D56" r:id="rId53" xr:uid="{F4D84986-13BB-45EA-A462-990756B14393}"/>
+    <hyperlink ref="D57" r:id="rId54" xr:uid="{7BE51B79-B6AB-45E9-BBB9-731D34FB7BB3}"/>
+    <hyperlink ref="D59" r:id="rId55" xr:uid="{DE5EA373-1BD8-4AA4-85B2-98AE217ED146}"/>
+    <hyperlink ref="D61" r:id="rId56" xr:uid="{32CF23CE-BDDE-4607-82FB-6016C37BFF4A}"/>
+    <hyperlink ref="D62" r:id="rId57" xr:uid="{C3A5EAFC-A1B3-4A5C-AAE2-F541243DFD31}"/>
+    <hyperlink ref="D63" r:id="rId58" xr:uid="{449BAD04-B74C-41A0-B610-5FA618AE4198}"/>
+    <hyperlink ref="D64" r:id="rId59" xr:uid="{F363159A-BF67-4495-8ED0-80D56AD499E0}"/>
+    <hyperlink ref="D65" r:id="rId60" xr:uid="{3C263FB0-D054-4F5E-ABAA-D15ED49EEA0D}"/>
+    <hyperlink ref="D66" r:id="rId61" xr:uid="{9DC156CB-4D80-4171-AFDA-052416CC5DB3}"/>
+    <hyperlink ref="D67" r:id="rId62" xr:uid="{B22FCE37-7C87-4D74-AF41-73DBB75A2940}"/>
+    <hyperlink ref="D68" r:id="rId63" xr:uid="{FA743FBE-E0D7-4448-B71D-462170D1EA44}"/>
+    <hyperlink ref="D24" r:id="rId64" xr:uid="{5BE34E04-4AF4-45CF-8970-63EE1EB23692}"/>
+    <hyperlink ref="D58" r:id="rId65" xr:uid="{2724C4CA-48CA-4E49-963D-2D9EA63A9AEA}"/>
+    <hyperlink ref="D60" r:id="rId66" xr:uid="{0101EBA4-577D-4274-8FDA-1C9A0AC0E50E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
